--- a/important_mails_2026-05-15.xlsx
+++ b/important_mails_2026-05-15.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,78 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 14 May 2026 02:39:33 +0000</t>
+          <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
+          <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的卖家，
+我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
+我们建议您提交所需的文件以取消禁止显示您的 ASIN 并激活您的列表。
+以下是您被屏蔽的 ASIN 的示例：
+B0F1R6Y4JL
+如果您想了解当前被禁止的所有 ASIN 以及被禁止的原因，请登录您的卖家中心帐户并转至 “目录“ &gt;&gt; “补全您的草稿“ &gt;&gt;“有问题的已发布商品信息“ &gt;&gt; “详情页面已删除“. 您所有的 ASIN 都将列在这里
+https://sellercentral-europe.amazon.com/fixyourproducts/drafts
+要上传所需文件或提出申诉以解除对 ASIN 的压制，请遵循此路径  登录您的卖家中心账户并前往 “绩效“ &gt;&gt; “帐户健康“ &gt;&gt; “文件要求“ 在下面 “产品合规要求“ 在右下角 &gt;&gt; “提供文件“ 并选择上传文件或上诉。
+https://sellercentral-europe.amazon.com/performance/account/health/compliance-request
+如果您需要进一步的帮助，请通过联系我们提交案例。- https://sellercentral-europe.amazon.com/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
+如果您不是正确的联系人，请将此电子邮件重定向到正确的联系人。
+如果您想退订，请回复所有主题行“退订”
+注意：此电子邮件不受监控，任何有问题的回复都不会得到答复
+请注意，所附表格属于亚马逊机密。不要打扰。
+感谢您在亚马逊商店销售，
+亚马逊购买团队
+在我们的 10 秒调查中分享快速反馈，无需登录供应商/卖家中心。您的意见很重要！
+单击此处，https://amazonexteu.qualtrics.com/jfe/form/SV_didQ0FJXzXequbQ?Condition=Singlelink&amp;caseId=${print-case-id}
+Amazon Services Europe S.à r.l.38 Avenue John F. Kennedy, L-1855 Luxembourg，卢森堡注册编号 B-93815，股本 37,551 欧元，营业执照编号： 132595，卢森堡增值税注册编号 LU 19647148。
+© 2022 Amazon.com Inc. 或其关联公司。保留所有权利</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 02:39:33 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -540,39 +597,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -588,39 +645,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -645,39 +702,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -693,39 +750,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -742,39 +799,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -794,39 +851,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -843,39 +900,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -900,40 +957,40 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -948,40 +1005,40 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -995,40 +1052,40 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1039,51 +1096,6 @@
 Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
 For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
 Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:37:14 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Votre facture pour les frais de paiement au titre de la REP pour
- les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
- for Amazon.fr sales</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Bonjour,
-Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
-La facture comprend (1) les frais d’éco-contribution qu’Amazon a payé en votre nom pour les ventes de produits soumis à des obligations REP sur Amazon.fr au cours de la période de référence applicable et (2) les frais de service REP Nous payons en votre nom, pour les catégories de REP spécifiées dans le résumé au niveau de la catégorie et dans le résumé au niveau de l’ASIN.
-Pour accéder à votre facture REP Nous Payons en votre nom , ouvrez la pièce jointe de cet e-mail ou accédez à la section Factures des frais du vendeur et recherchez « REP Nous payons en votre nom » dans la colonne « Type de facture ».
-Pour afficher un résumé au niveau de la catégorie des frais facturés, des périodes de déclaration applicables et des catégories REP, accédez à la section Affichage des transactions avec les frais de service comme type de transaction, et recherchez « REP Nous payons en votre nom » dans la colonne « Détails sur le produit ».
-Pour afficher le détail au niveau de l’ASIN de vos frais d’éco-contribution REP, des pério</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2423,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2426,390 +2438,21 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Fri, 8 May 2026 14:52:53 +0000</t>
+          <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>donotreply@amazon.com</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
+          <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 14:40:42 +0000</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
- Vendeur Amazon.com.be pour le mois de 4/2026)</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.com.be
- Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
-Nous vous écrivons pour vous informer que votre Facture Vendeur pour le mois de 4/2026 est maintenant disponible dans votre compte Seller Central.
-Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
-Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
-Pour toute question, contactez le Support Vendeur.
-Cordialement,
-Amazon.com.be</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 13:57:28 +0000</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 13:43:13 +0000</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
-Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
-För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
-På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
-Om du har några frågor, kontakta säljarsupport.
-Vänliga hälsningar,
-Amazon.se</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 13:40:52 +0000</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:55:06 +0000</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:49:29 +0000</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 8 May 2026 11:20:15 +0000</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
-Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
- 23,49 €
-https://www.amazon.de/gp/product/B0DRCB74YN/?ref_=
-Einkaufswagen anzeigen
-https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schaue dir weitere Optionen an
-75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
- 16,80 €
-https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
-100 * 150cm Feuerfeste Unterlage - Hitzebeständig bis 1800°F Hitzeschutzmatte - Grillteppich Bodenschutzmatte Grillmatten Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
- -17 % 25,19 € UVP: 30,24 €
-https://www.amazon.de/gp/product/B0BRTPDYMV/?ref_=ci_mcx_mr_2p_1_lm
-Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
- -4 % 20,15 € UVP: 20,97 €
-https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mc</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 9 May 2026 04:43:42 +0000</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-05-21</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2833,39 +2476,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2888,39 +2531,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -2929,39 +2572,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2981,39 +2624,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3033,39 +2676,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3085,39 +2728,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3138,39 +2781,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3190,39 +2833,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3242,39 +2885,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -3290,39 +2933,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3342,39 +2985,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -3390,39 +3033,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3439,39 +3082,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3491,39 +3134,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3543,39 +3186,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3592,39 +3235,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -3639,39 +3282,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3687,39 +3330,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3739,39 +3382,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3791,39 +3434,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3840,39 +3483,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3892,39 +3535,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3944,39 +3587,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3993,39 +3636,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4045,39 +3688,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -4091,39 +3734,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4143,39 +3786,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4192,39 +3835,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4240,39 +3883,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4292,39 +3935,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4341,39 +3984,84 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 11:37:14 +0000</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Votre facture pour les frais de paiement au titre de la REP pour
+ les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
+ for Amazon.fr sales</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Bonjour,
+Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
+La facture comprend (1) les frais d’éco-contribution qu’Amazon a payé en votre nom pour les ventes de produits soumis à des obligations REP sur Amazon.fr au cours de la période de référence applicable et (2) les frais de service REP Nous payons en votre nom, pour les catégories de REP spécifiées dans le résumé au niveau de la catégorie et dans le résumé au niveau de l’ASIN.
+Pour accéder à votre facture REP Nous Payons en votre nom , ouvrez la pièce jointe de cet e-mail ou accédez à la section Factures des frais du vendeur et recherchez « REP Nous payons en votre nom » dans la colonne « Type de facture ».
+Pour afficher un résumé au niveau de la catégorie des frais facturés, des périodes de déclaration applicables et des catégories REP, accédez à la section Affichage des transactions avec les frais de service comme type de transaction, et recherchez « REP Nous payons en votre nom » dans la colonne « Détails sur le produit ».
+Pour afficher le détail au niveau de l’ASIN de vos frais d’éco-contribution REP, des pério</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4392,39 +4080,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4448,39 +4136,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4498,39 +4186,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4548,39 +4236,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4598,39 +4286,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4648,39 +4336,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4698,39 +4386,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4746,39 +4434,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4796,39 +4484,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4846,39 +4534,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4888,39 +4576,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4941,39 +4629,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4989,39 +4677,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -5040,39 +4728,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -5083,39 +4771,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5134,39 +4822,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5185,39 +4873,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5236,39 +4924,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -5288,39 +4976,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -5349,39 +5037,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -5399,39 +5087,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5449,39 +5137,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5499,39 +5187,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -5545,39 +5233,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5595,40 +5283,40 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5645,40 +5333,40 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -5695,39 +5383,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -5761,39 +5449,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -5808,39 +5496,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -5856,39 +5544,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -5912,39 +5600,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -5963,6 +5651,322 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 14:52:53 +0000</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 14:40:42 +0000</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
+ Vendeur Amazon.com.be pour le mois de 4/2026)</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.com.be
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Vendeur pour le mois de 4/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 13:57:28 +0000</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 13:43:13 +0000</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 13:40:52 +0000</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 11:55:06 +0000</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 8 May 2026 11:49:29 +0000</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
@@ -5981,21 +5985,74 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Wed, 6 May 2026 15:00:42 +0000</t>
+          <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Votre paiement est en cours</t>
+          <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
+ 23,49 €
+https://www.amazon.de/gp/product/B0DRCB74YN/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
+ 16,80 €
+https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
+100 * 150cm Feuerfeste Unterlage - Hitzebeständig bis 1800°F Hitzeschutzmatte - Grillteppich Bodenschutzmatte Grillmatten Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
+ -17 % 25,19 € UVP: 30,24 €
+https://www.amazon.de/gp/product/B0BRTPDYMV/?ref_=ci_mcx_mr_2p_1_lm
+Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
+ -4 % 20,15 € UVP: 20,97 €
+https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mc</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 6 May 2026 15:00:42 +0000</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Votre paiement est en cours</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6010,39 +6067,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6061,39 +6118,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6115,39 +6172,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -6173,40 +6230,40 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6222,40 +6279,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6271,39 +6328,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6319,39 +6376,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6367,39 +6424,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6415,39 +6472,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6461,39 +6518,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -6511,40 +6568,40 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6560,39 +6617,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6608,39 +6665,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6656,40 +6713,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6705,39 +6762,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6754,39 +6811,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -6815,39 +6872,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6863,39 +6920,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6909,39 +6966,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -6956,39 +7013,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7008,39 +7065,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -7069,40 +7126,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -7115,39 +7172,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -7162,39 +7219,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -7207,40 +7264,40 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -7255,40 +7312,40 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -7302,39 +7359,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -7348,39 +7405,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -7395,39 +7452,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -7441,39 +7498,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -7488,39 +7545,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7535,39 +7592,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7586,39 +7643,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -7634,39 +7691,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -7687,39 +7744,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7737,40 +7794,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7788,39 +7845,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7837,39 +7894,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7887,40 +7944,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -7938,39 +7995,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -7988,39 +8045,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -8037,39 +8094,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8084,39 +8141,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8135,39 +8192,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -8185,39 +8242,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -8256,39 +8313,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -8304,40 +8361,40 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -8353,39 +8410,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -8401,39 +8458,39 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -8447,40 +8504,40 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -8496,39 +8553,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -8544,39 +8601,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8597,39 +8654,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8644,39 +8701,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -8693,39 +8750,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -8739,39 +8796,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -8790,40 +8847,40 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -8837,39 +8894,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8893,39 +8950,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -8949,39 +9006,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9002,39 +9059,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9056,39 +9113,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9111,39 +9168,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9164,39 +9221,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9219,39 +9276,39 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9281,39 +9338,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -9362,39 +9419,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -9403,39 +9460,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
